--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/90_workbooks/ISMS-IMP-A.5.31.5_Evidence_Register_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/90_workbooks/ISMS-IMP-A.5.31.5_Evidence_Register_20260208.xlsx
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>46001.49235933252</v>
+        <v>46001.51767944697</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>46426.49235933252</v>
+        <v>46426.51767944697</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="N2" s="4" t="n">
-        <v>46426.49235933252</v>
+        <v>46426.51767944697</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="3">
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>46016.49235933252</v>
+        <v>46016.51767944697</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>46426.49235933252</v>
+        <v>46426.51767944697</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="N3" s="4" t="n">
-        <v>46426.49235933252</v>
+        <v>46426.51767944697</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="4">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>45971.49235933252</v>
+        <v>45971.51767944697</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>46426.49235933252</v>
+        <v>46426.51767944697</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>46426.49235933252</v>
+        <v>46426.51767944697</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="5">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>45881.49235933252</v>
+        <v>45881.51767944697</v>
       </c>
       <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="6">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>46031.49235933252</v>
+        <v>46031.51767944697</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>46396.49235933252</v>
+        <v>46396.51767944697</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>46396.49235933252</v>
+        <v>46396.51767944697</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="7">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>46046.49235933252</v>
+        <v>46046.51767944697</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>46411.49235933252</v>
+        <v>46411.51767944697</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="N7" s="4" t="n">
-        <v>46411.49235933252</v>
+        <v>46411.51767944697</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="8">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>46056.49235933252</v>
+        <v>46056.51767944697</v>
       </c>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>46081.49235933252</v>
+        <v>46081.51767944697</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="9">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="10">
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>46051.49235933252</v>
+        <v>46051.51767944697</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>46141.49235933252</v>
+        <v>46141.51767944697</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>46081.49235933252</v>
+        <v>46081.51767944697</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="11">
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>46059.49235933252</v>
+        <v>46059.51767944697</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>46089.49235933252</v>
+        <v>46089.51767944697</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>46089.49235933252</v>
+        <v>46089.51767944697</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
     <row r="12">
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>45971.49235933252</v>
+        <v>45971.51767944697</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>46031.49235933252</v>
+        <v>46031.51767944697</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>46031.49235933252</v>
+        <v>46031.51767944697</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>46061.49235933252</v>
+        <v>46061.51767944697</v>
       </c>
     </row>
   </sheetData>
